--- a/control_file.xlsx
+++ b/control_file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maignac\20220704_Jupyter back-up\PS_results\Publishable\Files for publication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maignac\Price-setting-rep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EA87EC-02D5-483F-B298-A0D92EF71A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2008DCA7-EF57-4FE1-B7D3-38419FDDE28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{5F3F11B4-E44A-4804-8885-EB72D018B6C6}"/>
+    <workbookView xWindow="12435" yWindow="1095" windowWidth="16305" windowHeight="11295" firstSheet="1" activeTab="1" xr2:uid="{5F3F11B4-E44A-4804-8885-EB72D018B6C6}"/>
   </bookViews>
   <sheets>
     <sheet name="cover" sheetId="2" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="294">
   <si>
     <t>CONTROL FILE - EU electricity price-setting</t>
   </si>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>analysis start</t>
-  </si>
-  <si>
-    <t>END_2026</t>
   </si>
   <si>
     <t>H1 2026 cap (inclusive)</t>
@@ -951,6 +948,15 @@
   </si>
   <si>
     <t>platts</t>
+  </si>
+  <si>
+    <t>SCARCITY_FACTOR</t>
+  </si>
+  <si>
+    <t>multiplier on gas SRMC above which the price is classified as scarcity (step 7) by the algorithm. e.g. 1.5 = prices &gt;150% of gas SRMC</t>
+  </si>
+  <si>
+    <t>END_DATE</t>
   </si>
 </sst>
 </file>
@@ -1401,12 +1407,12 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1422,7 +1428,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1430,7 +1436,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -1438,7 +1444,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -1451,10 +1457,10 @@
     </row>
     <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1470,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -1478,7 +1484,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1486,7 +1492,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1502,7 +1508,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1545,10 +1551,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>23</v>
@@ -1556,10 +1562,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
         <v>179</v>
-      </c>
-      <c r="B2" t="s">
-        <v>180</v>
       </c>
       <c r="C2">
         <v>0.85</v>
@@ -1567,10 +1573,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C3">
         <v>0.25</v>
@@ -1578,10 +1584,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4">
         <v>0.85</v>
@@ -1589,10 +1595,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>0.5</v>
@@ -1600,10 +1606,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1611,10 +1617,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1622,10 +1628,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -1633,10 +1639,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="s">
         <v>187</v>
-      </c>
-      <c r="B9" t="s">
-        <v>188</v>
       </c>
       <c r="C9">
         <v>0.6</v>
@@ -1644,10 +1650,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C10">
         <v>0.85</v>
@@ -1655,10 +1661,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -1666,10 +1672,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1677,10 +1683,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -1698,7 +1704,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>22</v>
@@ -1709,582 +1715,582 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -2292,10 +2298,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -2303,10 +2309,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -2314,10 +2320,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C57">
         <v>1.5</v>
@@ -2325,10 +2331,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2336,10 +2342,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C59">
         <v>1.5</v>
@@ -2347,10 +2353,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -2358,10 +2364,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -2369,10 +2375,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C62">
         <v>3.5</v>
@@ -2380,10 +2386,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C63">
         <v>4</v>
@@ -2391,10 +2397,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C64">
         <v>4.5</v>
@@ -2402,10 +2408,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -2413,10 +2419,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C66">
         <v>4.5</v>
@@ -2424,10 +2430,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67">
         <v>5</v>
@@ -2435,10 +2441,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>2.5</v>
@@ -2446,10 +2452,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B69" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C69">
         <v>6</v>
@@ -2457,10 +2463,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -2468,10 +2474,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -2479,10 +2485,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -2490,10 +2496,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>2</v>
@@ -2501,10 +2507,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C74">
         <v>0.5</v>
@@ -2512,24 +2518,24 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>203</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
         <v>204</v>
-      </c>
-      <c r="B75" t="s">
-        <v>85</v>
-      </c>
-      <c r="C75" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>203</v>
+      </c>
+      <c r="B76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" t="s">
         <v>204</v>
-      </c>
-      <c r="B76" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2544,7 +2550,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>22</v>
@@ -2555,46 +2561,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
         <v>206</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>207</v>
-      </c>
-      <c r="C2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" t="s">
         <v>209</v>
-      </c>
-      <c r="C3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
         <v>211</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>212</v>
-      </c>
-      <c r="C4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" t="s">
         <v>214</v>
-      </c>
-      <c r="C5" t="s">
-        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2609,18 +2615,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" t="s">
         <v>216</v>
-      </c>
-      <c r="C1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -2631,7 +2637,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2642,7 +2648,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -2653,7 +2659,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2664,7 +2670,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B6">
         <v>4.5</v>
@@ -2675,7 +2681,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2696,24 +2702,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -2730,7 +2736,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2747,7 +2753,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2764,7 +2770,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2781,7 +2787,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2798,7 +2804,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2815,7 +2821,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2832,7 +2838,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2849,7 +2855,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2866,7 +2872,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2883,7 +2889,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2900,7 +2906,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2917,7 +2923,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2934,7 +2940,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2951,7 +2957,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2968,7 +2974,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2985,7 +2991,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3002,7 +3008,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3019,7 +3025,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3036,7 +3042,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3053,7 +3059,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3070,7 +3076,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3087,7 +3093,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3104,7 +3110,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3121,7 +3127,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3138,7 +3144,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3155,7 +3161,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3172,7 +3178,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3189,7 +3195,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3206,7 +3212,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3223,7 +3229,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3240,7 +3246,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3257,7 +3263,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3274,7 +3280,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3291,7 +3297,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -3308,7 +3314,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3325,7 +3331,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3342,7 +3348,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -3359,7 +3365,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -3376,7 +3382,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -3393,7 +3399,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -3410,7 +3416,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -3427,7 +3433,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -3444,7 +3450,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -3461,7 +3467,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3478,7 +3484,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3495,10 +3501,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C48">
         <v>0.32700000000000001</v>
@@ -3512,10 +3518,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49">
         <v>0.2666</v>
@@ -3529,10 +3535,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C50">
         <v>0.34720000000000001</v>
@@ -3546,10 +3552,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C51">
         <v>0.34720000000000001</v>
@@ -3563,10 +3569,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C52">
         <v>0.44379999999999997</v>
@@ -3580,10 +3586,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C53">
         <v>0.32900000000000001</v>
@@ -3597,10 +3603,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C54">
         <v>0.27</v>
@@ -3614,10 +3620,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55">
         <v>0.27</v>
@@ -3631,10 +3637,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56">
         <v>0.27</v>
@@ -3648,10 +3654,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C57">
         <v>0.27</v>
@@ -3665,10 +3671,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C58">
         <v>0.27</v>
@@ -3682,10 +3688,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C59">
         <v>0.27</v>
@@ -3699,10 +3705,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C60">
         <v>0.27</v>
@@ -3716,10 +3722,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C61">
         <v>0.27</v>
@@ -3733,10 +3739,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C62">
         <v>0.27</v>
@@ -3750,10 +3756,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C63">
         <v>0.4017</v>
@@ -3767,10 +3773,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64">
         <v>0.33579999999999999</v>
@@ -3784,10 +3790,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C65">
         <v>0.33700000000000002</v>
@@ -3801,10 +3807,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C66">
         <v>0.35</v>
@@ -3818,10 +3824,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C67">
         <v>0.28699999999999998</v>
@@ -3835,10 +3841,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C68">
         <v>0.33500000000000002</v>
@@ -3852,10 +3858,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C69">
         <v>0.33</v>
@@ -3869,10 +3875,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C70">
         <v>0.33100000000000002</v>
@@ -3886,10 +3892,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C71">
         <v>0.36499999999999999</v>
@@ -3903,10 +3909,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C72">
         <v>0.38</v>
@@ -3920,10 +3926,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C73">
         <v>0.311</v>
@@ -3937,10 +3943,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C74">
         <v>0.28999999999999998</v>
@@ -3954,10 +3960,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C75">
         <v>0.34</v>
@@ -3971,10 +3977,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C76">
         <v>0.23769999999999999</v>
@@ -3988,10 +3994,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C77">
         <v>0.30599999999999999</v>
@@ -4005,10 +4011,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C78">
         <v>0.2782</v>
@@ -4022,10 +4028,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C79">
         <v>0.27039999999999997</v>
@@ -4039,10 +4045,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C80">
         <v>0.29210000000000003</v>
@@ -4056,10 +4062,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C81">
         <v>0.32179999999999997</v>
@@ -4073,10 +4079,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C82">
         <v>0.31990000000000002</v>
@@ -4090,10 +4096,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C83">
         <v>0.43099999999999999</v>
@@ -4107,10 +4113,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C84">
         <v>0.25800000000000001</v>
@@ -4124,10 +4130,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C85">
         <v>0.31619999999999998</v>
@@ -4141,10 +4147,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86">
         <v>0.29499999999999998</v>
@@ -4158,10 +4164,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C87">
         <v>0.27</v>
@@ -4175,10 +4181,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C88">
         <v>0.30099999999999999</v>
@@ -4192,10 +4198,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B89" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C89">
         <v>0.28000000000000003</v>
@@ -4209,10 +4215,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C90">
         <v>0.38</v>
@@ -4226,10 +4232,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C91">
         <v>0.38</v>
@@ -4243,10 +4249,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C92">
         <v>0.36</v>
@@ -4260,10 +4266,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C93">
         <v>0.38</v>
@@ -4277,10 +4283,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B94" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C94">
         <v>0.23</v>
@@ -4294,10 +4300,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95">
         <v>0.23</v>
@@ -4311,10 +4317,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B96" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C96">
         <v>0.23</v>
@@ -4328,10 +4334,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C97">
         <v>0.34</v>
@@ -4345,10 +4351,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C98">
         <v>0.33399999999999991</v>
@@ -4362,10 +4368,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B99" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C99">
         <v>0.28000000000000003</v>
@@ -4379,10 +4385,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C100">
         <v>0.36</v>
@@ -4396,10 +4402,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C101">
         <v>0.34</v>
@@ -4413,10 +4419,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C102">
         <v>0.30399999999999999</v>
@@ -4430,10 +4436,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C103">
         <v>0.3289999999999999</v>
@@ -4447,10 +4453,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C104">
         <v>0.3289999999999999</v>
@@ -4464,10 +4470,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C105">
         <v>0.3289999999999999</v>
@@ -4481,10 +4487,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C106">
         <v>0.3289999999999999</v>
@@ -4498,10 +4504,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C107">
         <v>0.3289999999999999</v>
@@ -4515,10 +4521,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C108">
         <v>0.3289999999999999</v>
@@ -4532,10 +4538,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C109">
         <v>0.3289999999999999</v>
@@ -4549,10 +4555,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C110">
         <v>0.3289999999999999</v>
@@ -4566,10 +4572,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C111">
         <v>0.3289999999999999</v>
@@ -4583,10 +4589,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B112" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C112">
         <v>0.38</v>
@@ -4600,10 +4606,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C113">
         <v>0.36</v>
@@ -4617,10 +4623,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C114">
         <v>0.38</v>
@@ -4634,10 +4640,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C115">
         <v>0.36</v>
@@ -4651,10 +4657,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C116">
         <v>0.38</v>
@@ -4668,10 +4674,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C117">
         <v>0.38</v>
@@ -4685,10 +4691,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C118">
         <v>0.315</v>
@@ -4702,10 +4708,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C119">
         <v>0.315</v>
@@ -4719,10 +4725,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C120">
         <v>0.315</v>
@@ -4736,10 +4742,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B121" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C121">
         <v>0.315</v>
@@ -4753,10 +4759,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C122">
         <v>0.38</v>
@@ -4770,10 +4776,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>0.38</v>
@@ -4787,10 +4793,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C124">
         <v>0.32</v>
@@ -4804,10 +4810,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>0.33</v>
@@ -4821,10 +4827,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C126">
         <v>0.34</v>
@@ -4838,10 +4844,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B127" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C127">
         <v>0.28699999999999998</v>
@@ -4855,10 +4861,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B128" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C128">
         <v>0.33200000000000002</v>
@@ -4872,10 +4878,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B129" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C129">
         <v>0.3279999999999999</v>
@@ -4889,10 +4895,10 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C130">
         <v>0.32</v>
@@ -4906,10 +4912,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C131">
         <v>0.32</v>
@@ -4923,10 +4929,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C132">
         <v>0.36</v>
@@ -4940,10 +4946,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B133" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C133">
         <v>0.23</v>
@@ -4957,10 +4963,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C134">
         <v>0.42</v>
@@ -4974,10 +4980,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B135" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C135">
         <v>0.42</v>
@@ -4991,10 +4997,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C136">
         <v>0.29499999999999998</v>
@@ -5008,10 +5014,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C137">
         <v>0.371</v>
@@ -5025,10 +5031,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C138">
         <v>0.35799999999999998</v>
@@ -5042,10 +5048,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C139">
         <v>0.36</v>
@@ -5059,10 +5065,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C140">
         <v>0.33100000000000002</v>
@@ -5076,10 +5082,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C141">
         <v>0.33100000000000002</v>
@@ -5093,10 +5099,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B142" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C142">
         <v>0.33100000000000002</v>
@@ -5110,10 +5116,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C143">
         <v>0.33100000000000002</v>
@@ -5127,10 +5133,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C144">
         <v>0.33100000000000002</v>
@@ -5144,10 +5150,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B145" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C145">
         <v>0.33100000000000002</v>
@@ -5161,10 +5167,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B146" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C146">
         <v>0.33100000000000002</v>
@@ -5178,10 +5184,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B147" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C147">
         <v>0.33100000000000002</v>
@@ -5195,10 +5201,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B148" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C148">
         <v>0.33100000000000002</v>
@@ -5212,10 +5218,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B149" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C149">
         <v>0.36</v>
@@ -5229,10 +5235,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B150" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C150">
         <v>0.42</v>
@@ -5246,10 +5252,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C151">
         <v>0.32200000000000001</v>
@@ -5263,10 +5269,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C152">
         <v>0.42</v>
@@ -5280,10 +5286,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C153">
         <v>0.25700000000000001</v>
@@ -5297,10 +5303,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C154">
         <v>0.32</v>
@@ -5314,10 +5320,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B155" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C155">
         <v>0.34599999999999997</v>
@@ -5331,10 +5337,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B156" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C156">
         <v>0.34599999999999997</v>
@@ -5348,10 +5354,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B157" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C157">
         <v>0.34599999999999997</v>
@@ -5365,10 +5371,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B158" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C158">
         <v>0.34599999999999997</v>
@@ -5382,10 +5388,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B159" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C159">
         <v>0.34599999999999997</v>
@@ -5399,10 +5405,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B160" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C160">
         <v>0.34599999999999997</v>
@@ -5416,10 +5422,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B161" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C161">
         <v>0.34599999999999997</v>
@@ -5433,10 +5439,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B162" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C162">
         <v>0.34599999999999997</v>
@@ -5450,10 +5456,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B163" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C163">
         <v>0.34599999999999997</v>
@@ -5467,10 +5473,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B164" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C164">
         <v>0.34599999999999997</v>
@@ -5484,10 +5490,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C165">
         <v>0.34599999999999997</v>
@@ -5501,10 +5507,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B166" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C166">
         <v>0.34599999999999997</v>
@@ -5518,10 +5524,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B167" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C167">
         <v>0.34599999999999997</v>
@@ -5535,10 +5541,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B168" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C168">
         <v>0.34599999999999997</v>
@@ -5552,10 +5558,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B169" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C169">
         <v>0.34599999999999997</v>
@@ -5569,10 +5575,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B170" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C170">
         <v>0.34599999999999997</v>
@@ -5586,10 +5592,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B171" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C171">
         <v>0.34599999999999997</v>
@@ -5603,10 +5609,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C172">
         <v>0.34599999999999997</v>
@@ -5620,10 +5626,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B173" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C173">
         <v>0.34599999999999997</v>
@@ -5637,10 +5643,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B174" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C174">
         <v>0.34599999999999997</v>
@@ -5654,10 +5660,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B175" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C175">
         <v>0.34599999999999997</v>
@@ -5671,10 +5677,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B176" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C176">
         <v>0.34599999999999997</v>
@@ -5688,10 +5694,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B177" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C177">
         <v>0.34599999999999997</v>
@@ -5705,10 +5711,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B178" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C178">
         <v>0.34599999999999997</v>
@@ -5722,10 +5728,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B179" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C179">
         <v>0.34599999999999997</v>
@@ -5739,10 +5745,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B180" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C180">
         <v>0.34599999999999997</v>
@@ -5756,10 +5762,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B181" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C181">
         <v>0.34599999999999997</v>
@@ -5773,10 +5779,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B182" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C182">
         <v>0.34599999999999997</v>
@@ -5790,10 +5796,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B183" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C183">
         <v>0.34599999999999997</v>
@@ -5807,10 +5813,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B184" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C184">
         <v>0.34599999999999997</v>
@@ -5824,10 +5830,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B185" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C185">
         <v>0.34599999999999997</v>
@@ -5841,10 +5847,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B186" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C186">
         <v>0.34599999999999997</v>
@@ -5858,10 +5864,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B187" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C187">
         <v>0.34599999999999997</v>
@@ -5875,10 +5881,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B188" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C188">
         <v>0.34599999999999997</v>
@@ -5892,10 +5898,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B189" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C189">
         <v>0.34599999999999997</v>
@@ -5909,10 +5915,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B190" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C190">
         <v>0.34599999999999997</v>
@@ -5926,10 +5932,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B191" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C191">
         <v>0.34599999999999997</v>
@@ -5943,10 +5949,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B192" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C192">
         <v>0.34599999999999997</v>
@@ -5960,10 +5966,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B193" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C193">
         <v>0.34599999999999997</v>
@@ -5977,10 +5983,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B194" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C194">
         <v>0.25</v>
@@ -5994,10 +6000,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B195" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C195">
         <v>0.36430000000000001</v>
@@ -6011,10 +6017,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B196" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C196">
         <v>0.31140000000000001</v>
@@ -6028,10 +6034,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B197" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C197">
         <v>0.29880000000000001</v>
@@ -6045,10 +6051,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B198" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C198">
         <v>0.32229999999999998</v>
@@ -6062,10 +6068,10 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B199" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C199">
         <v>0.34010000000000001</v>
@@ -6079,10 +6085,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B200" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C200">
         <v>0.2727</v>
@@ -6096,10 +6102,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B201" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C201">
         <v>0.2727</v>
@@ -6113,10 +6119,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B202" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C202">
         <v>0.2923</v>
@@ -6130,10 +6136,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B203" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C203">
         <v>0.26690000000000003</v>
@@ -6147,10 +6153,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B204" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C204">
         <v>0.36159999999999998</v>
@@ -6164,10 +6170,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B205" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C205">
         <v>0.27710000000000001</v>
@@ -6181,10 +6187,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B206" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C206">
         <v>0.36980000000000002</v>
@@ -6198,10 +6204,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C207">
         <v>0.32090000000000002</v>
@@ -6215,10 +6221,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B208" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C208">
         <v>0.41510000000000002</v>
@@ -6232,10 +6238,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B209" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C209">
         <v>0.3281</v>
@@ -6249,10 +6255,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B210" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C210">
         <v>0.3281</v>
@@ -6266,10 +6272,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B211" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C211">
         <v>0.3281</v>
@@ -6283,10 +6289,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B212" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C212">
         <v>0.3281</v>
@@ -6300,10 +6306,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B213" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C213">
         <v>0.3281</v>
@@ -6317,10 +6323,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B214" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C214">
         <v>0.3281</v>
@@ -6334,10 +6340,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B215" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C215">
         <v>0.3281</v>
@@ -6351,10 +6357,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B216" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C216">
         <v>0.3281</v>
@@ -6368,10 +6374,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B217" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C217">
         <v>0.3281</v>
@@ -6385,10 +6391,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B218" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C218">
         <v>0.29320000000000002</v>
@@ -6402,10 +6408,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B219" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C219">
         <v>0.2626</v>
@@ -6419,10 +6425,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B220" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C220">
         <v>0.41710000000000003</v>
@@ -6436,10 +6442,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B221" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C221">
         <v>0.41710000000000003</v>
@@ -6453,10 +6459,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B222" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C222">
         <v>0.41710000000000003</v>
@@ -6470,10 +6476,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B223" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C223">
         <v>0.41710000000000003</v>
@@ -6487,10 +6493,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B224" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C224">
         <v>0.35010000000000002</v>
@@ -6504,10 +6510,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B225" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C225">
         <v>0.28000000000000003</v>
@@ -6531,82 +6537,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -6616,7 +6622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8AB0B9-F698-4DE9-A349-D40CDF2DF481}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -6654,7 +6660,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>293</v>
       </c>
       <c r="B3" s="6">
         <v>46203.958333333336</v>
@@ -6663,166 +6669,180 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>0.5</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>2025</v>
       </c>
       <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
         <v>49</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>50</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="b">
-        <v>0</v>
+        <v>291</v>
+      </c>
+      <c r="B11">
+        <v>1.5</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" t="s">
-        <v>291</v>
+        <v>52</v>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>222</v>
+      </c>
+      <c r="B13" t="s">
+        <v>290</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -6845,95 +6865,95 @@
         <v>22</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -6948,39 +6968,39 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -6988,10 +7008,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -7005,10 +7025,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -7022,10 +7042,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
@@ -7039,10 +7059,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -7051,7 +7071,7 @@
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -7059,10 +7079,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
       </c>
       <c r="C7" t="b">
         <v>1</v>
@@ -7071,10 +7091,10 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -7082,19 +7102,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -7102,10 +7122,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
         <v>81</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -7119,10 +7139,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -7136,10 +7156,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
@@ -7153,10 +7173,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
@@ -7170,10 +7190,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" t="b">
         <v>1</v>
@@ -7187,10 +7207,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" t="b">
         <v>1</v>
@@ -7204,10 +7224,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
@@ -7221,10 +7241,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" t="b">
         <v>1</v>
@@ -7238,10 +7258,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" t="b">
         <v>1</v>
@@ -7255,10 +7275,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" t="b">
         <v>1</v>
@@ -7272,10 +7292,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
         <v>92</v>
-      </c>
-      <c r="B19" t="s">
-        <v>93</v>
       </c>
       <c r="C19" t="b">
         <v>1</v>
@@ -7289,16 +7309,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" t="b">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -7306,10 +7326,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" t="b">
         <v>1</v>
@@ -7323,10 +7343,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" t="b">
         <v>1</v>
@@ -7340,10 +7360,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -7357,10 +7377,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" t="b">
         <v>1</v>
@@ -7374,10 +7394,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C25" t="b">
         <v>1</v>
@@ -7391,10 +7411,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" t="b">
         <v>1</v>
@@ -7408,10 +7428,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" t="b">
         <v>1</v>
@@ -7425,10 +7445,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
@@ -7442,10 +7462,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" t="b">
         <v>1</v>
@@ -7459,10 +7479,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" t="s">
         <v>105</v>
-      </c>
-      <c r="B30" t="s">
-        <v>106</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
@@ -7476,10 +7496,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" t="b">
         <v>0</v>
@@ -7493,10 +7513,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -7510,10 +7530,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
@@ -7527,10 +7547,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
@@ -7544,10 +7564,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C35" t="b">
         <v>1</v>
@@ -7556,7 +7576,7 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -7564,10 +7584,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C36" t="b">
         <v>1</v>
@@ -7581,10 +7601,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C37" t="b">
         <v>1</v>
@@ -7598,10 +7618,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
         <v>115</v>
-      </c>
-      <c r="B38" t="s">
-        <v>116</v>
       </c>
       <c r="C38" t="b">
         <v>1</v>
@@ -7615,10 +7635,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C39" t="b">
         <v>1</v>
@@ -7632,10 +7652,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C40" t="b">
         <v>1</v>
@@ -7649,10 +7669,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C41" t="b">
         <v>1</v>
@@ -7666,10 +7686,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C42" t="b">
         <v>1</v>
@@ -7683,10 +7703,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C43" t="b">
         <v>1</v>
@@ -7695,7 +7715,7 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
@@ -7703,10 +7723,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
@@ -7720,10 +7740,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
@@ -7737,10 +7757,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
@@ -7754,10 +7774,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
@@ -7781,1826 +7801,1826 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
         <v>80</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
         <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" t="s">
         <v>108</v>
-      </c>
-      <c r="B65" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" t="s">
         <v>117</v>
-      </c>
-      <c r="B81" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B103" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>101</v>
+      </c>
+      <c r="B112" t="s">
         <v>102</v>
-      </c>
-      <c r="B112" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>110</v>
+      </c>
+      <c r="B119" t="s">
         <v>111</v>
-      </c>
-      <c r="B119" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B121" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>75</v>
+      </c>
+      <c r="B123" t="s">
         <v>76</v>
-      </c>
-      <c r="B123" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B126" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B127" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B128" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B132" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B133" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B135" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B136" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B137" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B140" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B141" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B142" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B143" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>89</v>
+      </c>
+      <c r="B144" t="s">
         <v>90</v>
-      </c>
-      <c r="B144" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B145" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B146" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B147" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B148" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B149" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>120</v>
+      </c>
+      <c r="B150" t="s">
         <v>121</v>
-      </c>
-      <c r="B150" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B151" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B152" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B153" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B154" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B155" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B157" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B158" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B159" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B160" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B162" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B163" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B164" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B165" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B166" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>121</v>
+      </c>
+      <c r="B167" t="s">
         <v>122</v>
-      </c>
-      <c r="B167" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B168" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B169" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B172" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B173" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B174" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B175" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B176" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B177" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B178" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B179" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B180" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B181" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B182" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B183" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B184" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B185" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B187" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B188" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B189" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B190" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>95</v>
+      </c>
+      <c r="B191" t="s">
         <v>96</v>
-      </c>
-      <c r="B191" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B192" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B193" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B194" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B195" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B196" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B197" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B199" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B200" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B201" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B202" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B203" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B204" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B205" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B206" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>99</v>
+      </c>
+      <c r="B207" t="s">
         <v>100</v>
-      </c>
-      <c r="B207" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B208" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B209" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B210" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B213" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B214" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B215" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B216" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B217" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B219" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B220" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B221" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B222" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B223" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B225" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B226" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B227" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B228" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -9620,10 +9640,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>25</v>
@@ -9631,7 +9651,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -9640,192 +9660,192 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="B4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="8"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" t="s">
         <v>268</v>
-      </c>
-      <c r="B8" t="s">
-        <v>269</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11" s="8"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="8"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="8"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" t="s">
         <v>278</v>
-      </c>
-      <c r="B19" t="s">
-        <v>279</v>
       </c>
       <c r="C19" s="8"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" t="s">
         <v>280</v>
-      </c>
-      <c r="B20" t="s">
-        <v>281</v>
       </c>
       <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" t="s">
         <v>284</v>
-      </c>
-      <c r="B23" t="s">
-        <v>285</v>
       </c>
       <c r="C23" s="8"/>
     </row>
@@ -9850,42 +9870,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
         <v>134</v>
-      </c>
-      <c r="B2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
         <v>136</v>
-      </c>
-      <c r="B3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
         <v>138</v>
-      </c>
-      <c r="B4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -9893,135 +9913,135 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" t="s">
         <v>142</v>
-      </c>
-      <c r="B7" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" t="s">
         <v>144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" t="s">
         <v>146</v>
-      </c>
-      <c r="B10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" t="s">
         <v>148</v>
-      </c>
-      <c r="B11" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" t="s">
         <v>153</v>
-      </c>
-      <c r="B15" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -10036,10 +10056,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>23</v>
@@ -10050,7 +10070,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2">
         <v>48</v>
@@ -10061,7 +10081,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3">
         <v>0.20200000000000001</v>
@@ -10072,7 +10092,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -10080,10 +10100,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5">
         <v>25</v>
@@ -10091,10 +10111,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C6">
         <v>0.34100000000000003</v>
@@ -10102,10 +10122,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10113,10 +10133,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8">
         <v>11.9</v>
@@ -10124,10 +10144,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -10135,10 +10155,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10">
         <v>0.36399999999999999</v>
@@ -10146,10 +10166,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -10157,10 +10177,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C12">
         <v>8.9</v>
@@ -10168,10 +10188,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13">
         <v>8.77</v>
@@ -10179,10 +10199,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C14">
         <v>0.38500000000000001</v>
@@ -10190,10 +10210,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -10201,10 +10221,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C16">
         <v>40.4</v>
@@ -10212,10 +10232,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17">
         <v>0.27900000000000003</v>
@@ -10223,10 +10243,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -10234,10 +10254,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C19">
         <v>15.6</v>
@@ -10245,10 +10265,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20">
         <v>23.8</v>
@@ -10256,10 +10276,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -10267,10 +10287,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -10278,10 +10298,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C23">
         <v>60</v>
@@ -10289,10 +10309,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C24">
         <v>23</v>
@@ -10300,10 +10320,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -10311,10 +10331,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -10322,10 +10342,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C27">
         <v>39</v>
@@ -10333,10 +10353,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28">
         <v>0.20200000000000001</v>
@@ -10344,10 +10364,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -10355,10 +10375,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -10366,10 +10386,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -10377,10 +10397,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -10388,10 +10408,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C33">
         <v>0.32</v>
@@ -10399,10 +10419,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C34">
         <v>0.34499999999999997</v>
@@ -10423,18 +10443,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -10445,10 +10465,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -10456,10 +10476,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -10467,10 +10487,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -10478,10 +10498,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -10489,10 +10509,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -10500,10 +10520,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -10511,10 +10531,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -10522,10 +10542,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -10533,10 +10553,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -10544,10 +10564,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -10555,10 +10575,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -10566,10 +10586,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -10577,10 +10597,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -10588,10 +10608,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -10599,10 +10619,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -10610,10 +10630,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -10621,10 +10641,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -10632,7 +10652,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -10643,7 +10663,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -10654,7 +10674,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -10665,7 +10685,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -10676,90 +10696,90 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
